--- a/docs/design-docs/12_画面遷移設計書.xlsx
+++ b/docs/design-docs/12_画面遷移設計書.xlsx
@@ -10,7 +10,599 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面遷移設計書</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>システム名</t>
+  </si>
+  <si>
+    <t>電力設備巡視点検管理システム</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-TRANS-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>全画面遷移一覧</t>
+  </si>
+  <si>
+    <t>モジュール</t>
+  </si>
+  <si>
+    <t>遷移元</t>
+  </si>
+  <si>
+    <t>操作</t>
+  </si>
+  <si>
+    <t>遷移先</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>テスト経路ID</t>
+  </si>
+  <si>
+    <t>共通</t>
+  </si>
+  <si>
+    <t>ログイン</t>
+  </si>
+  <si>
+    <t>メインメニュー</t>
+  </si>
+  <si>
+    <t>画面遷移</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>設備マスタ</t>
+  </si>
+  <si>
+    <t>設備マスタ一覧</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>点検計画</t>
+  </si>
+  <si>
+    <t>年間点検計画一覧</t>
+  </si>
+  <si>
+    <t>T003</t>
+  </si>
+  <si>
+    <t>点検実施(当日)</t>
+  </si>
+  <si>
+    <t>点検実施一覧</t>
+  </si>
+  <si>
+    <t>T004</t>
+  </si>
+  <si>
+    <t>異常報告</t>
+  </si>
+  <si>
+    <t>異常報告一覧</t>
+  </si>
+  <si>
+    <t>T005</t>
+  </si>
+  <si>
+    <t>対応指示</t>
+  </si>
+  <si>
+    <t>対応指示一覧</t>
+  </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>部署管理</t>
+  </si>
+  <si>
+    <t>部署マスタ一覧</t>
+  </si>
+  <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>担当者管理</t>
+  </si>
+  <si>
+    <t>担当者マスタ一覧</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>休日管理</t>
+  </si>
+  <si>
+    <t>休日カレンダー一覧</t>
+  </si>
+  <si>
+    <t>T009</t>
+  </si>
+  <si>
+    <t>部品管理</t>
+  </si>
+  <si>
+    <t>保守部品一覧</t>
+  </si>
+  <si>
+    <t>T010</t>
+  </si>
+  <si>
+    <t>レポート</t>
+  </si>
+  <si>
+    <t>総合レポート</t>
+  </si>
+  <si>
+    <t>T011</t>
+  </si>
+  <si>
+    <t>マスタ</t>
+  </si>
+  <si>
+    <t>新規登録</t>
+  </si>
+  <si>
+    <t>設備マスタ登録</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
+    <t>設備code click</t>
+  </si>
+  <si>
+    <t>設備マスタ編集</t>
+  </si>
+  <si>
+    <t>T102</t>
+  </si>
+  <si>
+    <t>検索</t>
+  </si>
+  <si>
+    <t>同一画面(検索結果)</t>
+  </si>
+  <si>
+    <t>同一画面</t>
+  </si>
+  <si>
+    <t>T103</t>
+  </si>
+  <si>
+    <t>選択削除→confirm</t>
+  </si>
+  <si>
+    <t>同一画面(削除後)</t>
+  </si>
+  <si>
+    <t>T104</t>
+  </si>
+  <si>
+    <t>設備マスタ登録/編集</t>
+  </si>
+  <si>
+    <t>親設備選択</t>
+  </si>
+  <si>
+    <t>親設備Popup</t>
+  </si>
+  <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
+    <t>点検項目マスタ一覧</t>
+  </si>
+  <si>
+    <t>copy</t>
+  </si>
+  <si>
+    <t>同一画面(copy後)</t>
+  </si>
+  <si>
+    <t>T110</t>
+  </si>
+  <si>
+    <t>並順▲/▼</t>
+  </si>
+  <si>
+    <t>同一画面(並替後)</t>
+  </si>
+  <si>
+    <t>T111</t>
+  </si>
+  <si>
+    <t>点検</t>
+  </si>
+  <si>
+    <t>点検計画登録Wizard</t>
+  </si>
+  <si>
+    <t>Step1→進む</t>
+  </si>
+  <si>
+    <t>Step2</t>
+  </si>
+  <si>
+    <t>T203</t>
+  </si>
+  <si>
+    <t>Step2→戻る</t>
+  </si>
+  <si>
+    <t>Step1</t>
+  </si>
+  <si>
+    <t>T204</t>
+  </si>
+  <si>
+    <t>Step3→戻る</t>
+  </si>
+  <si>
+    <t>T206</t>
+  </si>
+  <si>
+    <t>Step3→進む</t>
+  </si>
+  <si>
+    <t>Step4(確認)</t>
+  </si>
+  <si>
+    <t>T207</t>
+  </si>
+  <si>
+    <t>Step4→確定</t>
+  </si>
+  <si>
+    <t>T209</t>
+  </si>
+  <si>
+    <t>Step4→一時保存</t>
+  </si>
+  <si>
+    <t>Step4(保存完了)</t>
+  </si>
+  <si>
+    <t>T210</t>
+  </si>
+  <si>
+    <t>点検実施一覧(当日)</t>
+  </si>
+  <si>
+    <t>行click</t>
+  </si>
+  <si>
+    <t>点検実施入力</t>
+  </si>
+  <si>
+    <t>T211</t>
+  </si>
+  <si>
+    <t>異常報告へ(異常あり)</t>
+  </si>
+  <si>
+    <t>異常報告登録</t>
+  </si>
+  <si>
+    <t>T213</t>
+  </si>
+  <si>
+    <t>点検実施詳細</t>
+  </si>
+  <si>
+    <t>修正申請</t>
+  </si>
+  <si>
+    <t>同一画面(申請中)</t>
+  </si>
+  <si>
+    <t>T214</t>
+  </si>
+  <si>
+    <t>点検実施承認一覧</t>
+  </si>
+  <si>
+    <t>一括承認→confirm</t>
+  </si>
+  <si>
+    <t>同一画面(通知)</t>
+  </si>
+  <si>
+    <t>T215</t>
+  </si>
+  <si>
+    <t>一括差戻→理由</t>
+  </si>
+  <si>
+    <t>T216</t>
+  </si>
+  <si>
+    <t>異常</t>
+  </si>
+  <si>
+    <t>検索条件保存</t>
+  </si>
+  <si>
+    <t>T302</t>
+  </si>
+  <si>
+    <t>異常報告詳細</t>
+  </si>
+  <si>
+    <t>調査開始(未了→調査中)</t>
+  </si>
+  <si>
+    <t>同一画面(調査中)</t>
+  </si>
+  <si>
+    <t>T306</t>
+  </si>
+  <si>
+    <t>対応開始(調査中→対応中)</t>
+  </si>
+  <si>
+    <t>同一画面(対応中)</t>
+  </si>
+  <si>
+    <t>T307</t>
+  </si>
+  <si>
+    <t>完了(対応中→完了)</t>
+  </si>
+  <si>
+    <t>同一画面(完了)</t>
+  </si>
+  <si>
+    <t>T308</t>
+  </si>
+  <si>
+    <t>close</t>
+  </si>
+  <si>
+    <t>T309</t>
+  </si>
+  <si>
+    <t>再発防止策登録</t>
+  </si>
+  <si>
+    <t>是正処置報告書</t>
+  </si>
+  <si>
+    <t>T310</t>
+  </si>
+  <si>
+    <t>対応</t>
+  </si>
+  <si>
+    <t>対応指示登録</t>
+  </si>
+  <si>
+    <t>行追加</t>
+  </si>
+  <si>
+    <t>同一画面(行追加後)</t>
+  </si>
+  <si>
+    <t>T401</t>
+  </si>
+  <si>
+    <t>行削除</t>
+  </si>
+  <si>
+    <t>同一画面(行削除後)</t>
+  </si>
+  <si>
+    <t>T402</t>
+  </si>
+  <si>
+    <t>担当者選択→Popup→反映</t>
+  </si>
+  <si>
+    <t>T403</t>
+  </si>
+  <si>
+    <t>登録→成功</t>
+  </si>
+  <si>
+    <t>T404</t>
+  </si>
+  <si>
+    <t>印刷用表示</t>
+  </si>
+  <si>
+    <t>印刷用別window</t>
+  </si>
+  <si>
+    <t>新規window</t>
+  </si>
+  <si>
+    <t>T405</t>
+  </si>
+  <si>
+    <t>対応指示詳細</t>
+  </si>
+  <si>
+    <t>完了報告(明細)</t>
+  </si>
+  <si>
+    <t>同一画面(展開)</t>
+  </si>
+  <si>
+    <t>T407</t>
+  </si>
+  <si>
+    <t>保存→全明細完了</t>
+  </si>
+  <si>
+    <t>同一画面(自動完了)</t>
+  </si>
+  <si>
+    <t>T408</t>
+  </si>
+  <si>
+    <t>承認申請</t>
+  </si>
+  <si>
+    <t>T409</t>
+  </si>
+  <si>
+    <t>組織</t>
+  </si>
+  <si>
+    <t>部署マスタ登録/編集</t>
+  </si>
+  <si>
+    <t>上位部署→Popup</t>
+  </si>
+  <si>
+    <t>T503</t>
+  </si>
+  <si>
+    <t>一括lock/解除</t>
+  </si>
+  <si>
+    <t>同一画面(更新後)</t>
+  </si>
+  <si>
+    <t>T504</t>
+  </si>
+  <si>
+    <t>calendar</t>
+  </si>
+  <si>
+    <t>休日登録/編集</t>
+  </si>
+  <si>
+    <t>範囲指定一括登録</t>
+  </si>
+  <si>
+    <t>T602</t>
+  </si>
+  <si>
+    <t>保守</t>
+  </si>
+  <si>
+    <t>新規/編集</t>
+  </si>
+  <si>
+    <t>保守部品登録/編集</t>
+  </si>
+  <si>
+    <t>T701</t>
+  </si>
+  <si>
+    <t>期間指定→表示</t>
+  </si>
+  <si>
+    <t>同一画面(集計表示)</t>
+  </si>
+  <si>
+    <t>T801</t>
+  </si>
+  <si>
+    <t>T802</t>
+  </si>
+  <si>
+    <t>経路数集計</t>
+  </si>
+  <si>
+    <t>総経路数</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>画面遷移(画面間)</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>同一画面更新</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
